--- a/data/trans_orig/IBSE_100-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IBSE_100-Clase-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>79,85</t>
+          <t>80,02</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>79,68</t>
+          <t>79,42</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79,77</t>
+          <t>79,74</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>78,19; 81,33</t>
+          <t>78,52; 81,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>78,3; 81,1</t>
+          <t>78,1; 80,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,75; 80,78</t>
+          <t>78,68; 80,72</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>79,87</t>
+          <t>80,03</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78,52</t>
+          <t>78,58</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>78,08; 81,37</t>
+          <t>78,3; 81,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>75,33; 78,34</t>
+          <t>75,59; 78,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77,43; 79,61</t>
+          <t>77,43; 79,6</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>82,02</t>
+          <t>78,83</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>73,52</t>
+          <t>74,03</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80,33</t>
+          <t>77,47</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>77,94; 85,92</t>
+          <t>77,21; 80,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71,26; 75,61</t>
+          <t>71,74; 76,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76,63; 84,51</t>
+          <t>75,97; 78,57</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>76,52</t>
+          <t>76,57</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>76,56</t>
+          <t>75,32</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76,54</t>
+          <t>76,03</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>75,3; 77,62</t>
+          <t>75,31; 77,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>74,96; 78,82</t>
+          <t>74,23; 76,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75,56; 77,92</t>
+          <t>75,13; 76,81</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>72,82</t>
+          <t>72,75</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>70,17</t>
+          <t>68,57</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>71,13</t>
+          <t>70,27</t>
         </is>
       </c>
     </row>
@@ -771,24 +771,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>71,0; 74,63</t>
+          <t>71,04; 74,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,2; 73,62</t>
+          <t>67,31; 69,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,76; 73,43</t>
+          <t>69,25; 71,26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -798,17 +798,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>86,89</t>
+          <t>87,2</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>72,92</t>
+          <t>73,04</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76,29</t>
+          <t>76,16</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>84,04; 89,47</t>
+          <t>84,53; 89,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>71,53; 74,18</t>
+          <t>71,72; 74,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74,97; 77,76</t>
+          <t>74,84; 77,49</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>78,78</t>
+          <t>78,03</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>74,59</t>
+          <t>73,95</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>76,63</t>
+          <t>75,94</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>77,81; 80,87</t>
+          <t>77,39; 78,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>73,85; 75,84</t>
+          <t>73,38; 74,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>75,97; 78,07</t>
+          <t>75,49; 76,39</t>
         </is>
       </c>
     </row>
